--- a/performance_review/성과_고과_시스템.xlsx
+++ b/performance_review/성과_고과_시스템.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -571,14 +571,14 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ④ '계산_순위표' 시트가 자가점검표의 정량 항목만으로 성과/역량/동료평가 점수를 계산하고 순위를 매깁니다.</t>
+          <t xml:space="preserve">  ④ '계산_순위표' 시트가 자가점검표의 정량 항목으로 '자가점검 기준점수'를 계산합니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ⑤ '1on1_준비노트' 시트에 리뷰 전 참고할 메모를 자유롭게 남길 수 있습니다 (점수에는 반영되지 않음).</t>
+          <t xml:space="preserve">  ⑤ 팀장이 '1on1_준비노트' 시트에서 필요한 경우에만 조정점수(-10~+10)를 매기고 리뷰 메모를 남깁니다. 이 조정점수가 기준점수에 더해져 최종점수가 됩니다.</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
     <row r="16">
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>3. 모든 항목이 정량화된 이유</t>
+          <t>3. 모든 항목이 정량화된 이유 + 최소한의 팀장 검수</t>
         </is>
       </c>
     </row>
@@ -640,98 +640,112 @@
     <row r="18">
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 팀장의 별도 정성평가(1~5점) 단계 없이, 자가점검표의 정량 항목만으로 최종 점수가 자동 계산됩니다.</t>
+          <t xml:space="preserve">  - 자가점검 항목의 가중합인 '자가점검 기준점수'는 전적으로 정량 항목으로만 계산됩니다.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - '1on1_준비노트' 시트는 점수와 무관한 리뷰 준비용 메모입니다.</t>
+          <t xml:space="preserve">  - 다만 자가점수 부풀리기를 막기 위해, 팀장이 '1on1_준비노트'에서 -10~+10점의 소폭 조정점수를 매길 수 있습니다(가중치 없이 그대로 더해짐, 기본값 0).</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="3" t="inlineStr"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 1~5점짜리 별도 정성평가 항목은 두지 않습니다 — 조정점수는 어디까지나 자가점검 결과에 대한 보정입니다.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>4. 신규 구성원 추가 방법</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ① '자가점검표_템플릿' 시트를 복제하고 시트명을 '자가점검표_홍길동'처럼 '자가점검표_&lt;이름&gt;'으로 변경</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">  ① '자가점검표_템플릿' 시트를 복제하고 시트명을 '자가점검표_홍길동'처럼 '자가점검표_&lt;이름&gt;'으로 변경</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">  ② '동료추천_집계', '1on1_준비노트', '계산_순위표' 각 표의 마지막 행 아래에 새 행을 추가하고, 이름 칸에 이름을 입력한 뒤 윗 행의 수식을 그대로 복사(드래그)합니다.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="3" t="inlineStr"/>
-    </row>
     <row r="25">
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>5. 점수 산식 (파라미터 시트에서 가중치 조정 가능)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 성과환산점수(100) = AVERAGE(중점과제1~3 점수, 추가과제 점수, 아쉬운성과 점수, 기여도 점수, 성과도 점수) × 10   (7개 항목 동일 가중치 평균)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 역량환산점수(100) = 전문성강화 점수(1~10→40점) + 학점환산(SKHU+mySuni, 상한 20학점→30점) + AI자가점수(1~10→30점)</t>
+          <t xml:space="preserve">  - 성과환산점수(100) = AVERAGE(중점과제1~3 점수, 추가과제 점수, 아쉬운성과 점수, 기여도 점수, 성과도 점수) × 10   (7개 항목 동일 가중치 평균)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 동료환산점수(100) = MIN(추천받은 횟수, 상한 4회) / 4 × 100</t>
+          <t xml:space="preserve">  - 역량환산점수(100) = 전문성강화 점수(1~10→40점) + 학점환산(SKHU+mySuni, 상한 20학점→30점) + AI자가점수(1~10→30점)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 최종점수 = 성과환산×60% + 역량환산×20% + 동료환산×20% (기본값, '파라미터' 시트에서 조정 가능)</t>
+          <t xml:space="preserve">  - 동료환산점수(100) = MIN(추천받은 횟수, 상한 4회) / 4 × 100</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="3" t="inlineStr"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 자가점검 기준점수 = 성과환산×60% + 역량환산×20% + 동료환산×20% (기본값, '파라미터' 시트에서 조정 가능)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 최종점수 = MAX(0, MIN(100, 자가점검 기준점수 + 팀장 조정점수))</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>6. 참고</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="3" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  - 이 워크북은 완전 오프라인으로 동작하며 외부 네트워크 연결이 필요하지 않습니다.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="3" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  - ranking_dashboard.html은 구성원 개인 자가점검표(.xlsx) 여러 개를 한 번에 업로드해 전체 통계와 개인별 1:1 화면을 보여줍니다.</t>
         </is>
@@ -751,7 +765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -771,8 +785,10 @@
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -870,10 +886,20 @@
       </c>
       <c r="R3" s="12" t="inlineStr">
         <is>
+          <t>자가점검 기준점수(100)</t>
+        </is>
+      </c>
+      <c r="S3" s="12" t="inlineStr">
+        <is>
+          <t>팀장조정점수</t>
+        </is>
+      </c>
+      <c r="T3" s="12" t="inlineStr">
+        <is>
           <t>최종점수</t>
         </is>
       </c>
-      <c r="S3" s="12" t="inlineStr">
+      <c r="U3" s="12" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
@@ -953,8 +979,16 @@
         <f>J4*파라미터!$B$4+O4*파라미터!$B$5+Q4*파라미터!$B$6</f>
         <v/>
       </c>
-      <c r="S4" s="17">
-        <f>RANK(R4,$R$4:$R$7,0)</f>
+      <c r="S4" s="16">
+        <f>'1on1_준비노트'!C5</f>
+        <v/>
+      </c>
+      <c r="T4" s="16">
+        <f>MAX(0,MIN(100,R4+S4))</f>
+        <v/>
+      </c>
+      <c r="U4" s="17">
+        <f>RANK(T4,$T$4:$T$7,0)</f>
         <v/>
       </c>
     </row>
@@ -1032,8 +1066,16 @@
         <f>J5*파라미터!$B$4+O5*파라미터!$B$5+Q5*파라미터!$B$6</f>
         <v/>
       </c>
-      <c r="S5" s="17">
-        <f>RANK(R5,$R$4:$R$7,0)</f>
+      <c r="S5" s="16">
+        <f>'1on1_준비노트'!C6</f>
+        <v/>
+      </c>
+      <c r="T5" s="16">
+        <f>MAX(0,MIN(100,R5+S5))</f>
+        <v/>
+      </c>
+      <c r="U5" s="17">
+        <f>RANK(T5,$T$4:$T$7,0)</f>
         <v/>
       </c>
     </row>
@@ -1111,8 +1153,16 @@
         <f>J6*파라미터!$B$4+O6*파라미터!$B$5+Q6*파라미터!$B$6</f>
         <v/>
       </c>
-      <c r="S6" s="17">
-        <f>RANK(R6,$R$4:$R$7,0)</f>
+      <c r="S6" s="16">
+        <f>'1on1_준비노트'!C7</f>
+        <v/>
+      </c>
+      <c r="T6" s="16">
+        <f>MAX(0,MIN(100,R6+S6))</f>
+        <v/>
+      </c>
+      <c r="U6" s="17">
+        <f>RANK(T6,$T$4:$T$7,0)</f>
         <v/>
       </c>
     </row>
@@ -1190,8 +1240,16 @@
         <f>J7*파라미터!$B$4+O7*파라미터!$B$5+Q7*파라미터!$B$6</f>
         <v/>
       </c>
-      <c r="S7" s="17">
-        <f>RANK(R7,$R$4:$R$7,0)</f>
+      <c r="S7" s="16">
+        <f>'1on1_준비노트'!C8</f>
+        <v/>
+      </c>
+      <c r="T7" s="16">
+        <f>MAX(0,MIN(100,R7+S7))</f>
+        <v/>
+      </c>
+      <c r="U7" s="17">
+        <f>RANK(T7,$T$4:$T$7,0)</f>
         <v/>
       </c>
     </row>
@@ -1204,10 +1262,10 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A10:S10"/>
+    <mergeCell ref="A10:U10"/>
+    <mergeCell ref="A1:U1"/>
   </mergeCells>
-  <conditionalFormatting sqref="R4:R7">
+  <conditionalFormatting sqref="T4:T7">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -3963,106 +4021,138 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>1:1 리뷰 준비 노트 (점수에는 반영되지 않는 참고용 메모)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+          <t>1:1 리뷰 준비 노트 + 팀장 조정점수</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>조정점수는 자가점수 부풀리기를 막기 위한 소폭 보정용입니다(-10~+10, 가중치 없이 최종점수에 그대로 더해짐). 특별한 사유가 없으면 0으로 둡니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>이름</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>파트</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>팀장 조정점수(-10~+10)</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>1:1 준비 메모</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>홍길동</t>
-        </is>
-      </c>
-      <c r="B4" s="13">
-        <f>INDIRECT("'자가점검표_"&amp;A4&amp;"'!B4")</f>
-        <v/>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>핵심 과제 초과달성 축하. 설비 매뉴얼 지연 원인과 재발방지 계획을 함께 점검.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>김영희</t>
+          <t>홍길동</t>
         </is>
       </c>
       <c r="B5" s="13">
         <f>INDIRECT("'자가점검표_"&amp;A5&amp;"'!B4")</f>
         <v/>
       </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>품질 체계 개선 성과 우수. 전사 확산 계획을 함께 수립.</t>
+      <c r="C5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>핵심 과제 초과달성 축하. 설비 매뉴얼 지연 원인과 재발방지 계획을 함께 점검.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>이철수</t>
+          <t>김영희</t>
         </is>
       </c>
       <c r="B6" s="13">
         <f>INDIRECT("'자가점검표_"&amp;A6&amp;"'!B4")</f>
         <v/>
       </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>계획 수행은 양호. 현업 의견수렴 프로세스 보완 방안 논의.</t>
+      <c r="C6" s="10" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>품질 체계 개선 성과 우수. 다만 일부 자가점수가 다소 후한 편으로 보여 소폭 하향 조정. 전사 확산 계획을 함께 수립.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>박민수</t>
+          <t>이철수</t>
         </is>
       </c>
       <c r="B7" s="13">
         <f>INDIRECT("'자가점검표_"&amp;A7&amp;"'!B4")</f>
         <v/>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>계획 수행은 견고했으나 자가점수가 다소 박한 편으로 보여 상향 조정. 현업 의견수렴 프로세스 보완 방안 논의.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>박민수</t>
+        </is>
+      </c>
+      <c r="B8" s="13">
+        <f>INDIRECT("'자가점검표_"&amp;A8&amp;"'!B4")</f>
+        <v/>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>R&amp;D 로드맵 성과 확인. 신청서 품질 관리 프로세스 논의.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="C5 C6 C7 C8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="-10~10 사이의 정수를 입력하세요." type="whole" operator="between">
+      <formula1>-10</formula1>
+      <formula2>10</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/performance_review/성과_고과_시스템.xlsx
+++ b/performance_review/성과_고과_시스템.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -654,98 +654,112 @@
     <row r="20">
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 1~5점짜리 별도 정성평가 항목은 두지 않습니다 — 조정점수는 어디까지나 자가점검 결과에 대한 보정입니다.</t>
+          <t xml:space="preserve">  - 동료에게 추천받은 구성원에게는 추천 1회당 +1점의 추천가산점이 상한 없이 별도로 더해집니다(동료환산점수 20% 가중치와는 별개).</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="3" t="inlineStr"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 1~5점짜리 별도 정성평가 항목은 두지 않습니다 — 조정점수·가산점은 어디까지나 자가점검 결과에 대한 보정입니다.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>4. 신규 구성원 추가 방법</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ① '자가점검표_템플릿' 시트를 복제하고 시트명을 '자가점검표_홍길동'처럼 '자가점검표_&lt;이름&gt;'으로 변경</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">  ① '자가점검표_템플릿' 시트를 복제하고 시트명을 '자가점검표_홍길동'처럼 '자가점검표_&lt;이름&gt;'으로 변경</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">  ② '동료추천_집계', '1on1_준비노트', '계산_순위표' 각 표의 마지막 행 아래에 새 행을 추가하고, 이름 칸에 이름을 입력한 뒤 윗 행의 수식을 그대로 복사(드래그)합니다.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="3" t="inlineStr"/>
-    </row>
     <row r="26">
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>5. 점수 산식 (파라미터 시트에서 가중치 조정 가능)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 성과환산점수(100) = AVERAGE(중점과제1~3 점수, 추가과제 점수, 아쉬운성과 점수, 기여도 점수, 성과도 점수) × 10   (7개 항목 동일 가중치 평균)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 역량환산점수(100) = 전문성강화 점수(1~10→40점) + 학점환산(SKHU+mySuni, 상한 20학점→30점) + AI자가점수(1~10→30점)</t>
+          <t xml:space="preserve">  - 성과환산점수(100) = AVERAGE(중점과제1~3 점수, 추가과제 점수, 아쉬운성과 점수, 기여도 점수, 성과도 점수) × 10   (7개 항목 동일 가중치 평균)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 동료환산점수(100) = MIN(추천받은 횟수, 상한 4회) / 4 × 100</t>
+          <t xml:space="preserve">  - 역량환산점수(100) = 전문성강화 점수(1~10→40점) + 학점환산(SKHU+mySuni, 상한 20학점→30점) + AI자가점수(1~10→30점)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 자가점검 기준점수 = 성과환산×60% + 역량환산×20% + 동료환산×20% (기본값, '파라미터' 시트에서 조정 가능)</t>
+          <t xml:space="preserve">  - 동료환산점수(100) = MIN(추천받은 횟수, 상한 4회) / 4 × 100</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 최종점수 = MAX(0, MIN(100, 자가점검 기준점수 + 팀장 조정점수))</t>
+          <t xml:space="preserve">  - 자가점검 기준점수 = 성과환산×60% + 역량환산×20% + 동료환산×20% (기본값, '파라미터' 시트에서 조정 가능)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="3" t="inlineStr"/>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 추천가산점 = 추천받은 횟수 × 1점 (상한 없음, 동료환산점수 20% 가중치와 별개로 추가되는 보너스)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 최종점수 = MAX(0, MIN(100, 자가점검 기준점수 + 팀장 조정점수 + 추천가산점))</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>6. 참고</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="3" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  - 이 워크북은 완전 오프라인으로 동작하며 외부 네트워크 연결이 필요하지 않습니다.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="3" t="inlineStr">
+    <row r="37">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  - ranking_dashboard.html은 구성원 개인 자가점검표(.xlsx) 여러 개를 한 번에 업로드해 전체 통계와 개인별 1:1 화면을 보여줍니다.</t>
         </is>
@@ -765,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U10"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -788,7 +802,8 @@
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -896,10 +911,15 @@
       </c>
       <c r="T3" s="12" t="inlineStr">
         <is>
+          <t>추천가산점</t>
+        </is>
+      </c>
+      <c r="U3" s="12" t="inlineStr">
+        <is>
           <t>최종점수</t>
         </is>
       </c>
-      <c r="U3" s="12" t="inlineStr">
+      <c r="V3" s="12" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
@@ -984,11 +1004,15 @@
         <v/>
       </c>
       <c r="T4" s="16">
-        <f>MAX(0,MIN(100,R4+S4))</f>
-        <v/>
-      </c>
-      <c r="U4" s="17">
-        <f>RANK(T4,$T$4:$T$7,0)</f>
+        <f>P4</f>
+        <v/>
+      </c>
+      <c r="U4" s="16">
+        <f>MAX(0,MIN(100,R4+S4+T4))</f>
+        <v/>
+      </c>
+      <c r="V4" s="17">
+        <f>RANK(U4,$U$4:$U$7,0)</f>
         <v/>
       </c>
     </row>
@@ -1071,11 +1095,15 @@
         <v/>
       </c>
       <c r="T5" s="16">
-        <f>MAX(0,MIN(100,R5+S5))</f>
-        <v/>
-      </c>
-      <c r="U5" s="17">
-        <f>RANK(T5,$T$4:$T$7,0)</f>
+        <f>P5</f>
+        <v/>
+      </c>
+      <c r="U5" s="16">
+        <f>MAX(0,MIN(100,R5+S5+T5))</f>
+        <v/>
+      </c>
+      <c r="V5" s="17">
+        <f>RANK(U5,$U$4:$U$7,0)</f>
         <v/>
       </c>
     </row>
@@ -1158,11 +1186,15 @@
         <v/>
       </c>
       <c r="T6" s="16">
-        <f>MAX(0,MIN(100,R6+S6))</f>
-        <v/>
-      </c>
-      <c r="U6" s="17">
-        <f>RANK(T6,$T$4:$T$7,0)</f>
+        <f>P6</f>
+        <v/>
+      </c>
+      <c r="U6" s="16">
+        <f>MAX(0,MIN(100,R6+S6+T6))</f>
+        <v/>
+      </c>
+      <c r="V6" s="17">
+        <f>RANK(U6,$U$4:$U$7,0)</f>
         <v/>
       </c>
     </row>
@@ -1245,11 +1277,15 @@
         <v/>
       </c>
       <c r="T7" s="16">
-        <f>MAX(0,MIN(100,R7+S7))</f>
-        <v/>
-      </c>
-      <c r="U7" s="17">
-        <f>RANK(T7,$T$4:$T$7,0)</f>
+        <f>P7</f>
+        <v/>
+      </c>
+      <c r="U7" s="16">
+        <f>MAX(0,MIN(100,R7+S7+T7))</f>
+        <v/>
+      </c>
+      <c r="V7" s="17">
+        <f>RANK(U7,$U$4:$U$7,0)</f>
         <v/>
       </c>
     </row>
@@ -1262,10 +1298,10 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A10:U10"/>
-    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="A10:V10"/>
+    <mergeCell ref="A1:V1"/>
   </mergeCells>
-  <conditionalFormatting sqref="T4:T7">
+  <conditionalFormatting sqref="U4:U7">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
